--- a/AAII_Financials/Quarterly/STLA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/STLA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>STLA</t>
   </si>
@@ -656,229 +656,241 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45473</v>
       </c>
       <c r="K7" s="2">
         <v>45473</v>
       </c>
       <c r="L7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>49676700</v>
+      </c>
+      <c r="E8" s="3">
         <v>43966300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46522800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>46490100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>45153300</v>
+      </c>
+      <c r="I8" s="3">
         <v>38708400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>37199000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>40074200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>45546400</v>
       </c>
       <c r="K8" s="3">
         <v>45546400</v>
       </c>
       <c r="L8" s="3">
+        <v>45546400</v>
+      </c>
+      <c r="M8" s="3">
         <v>45860900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>50390200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>48251500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>53694300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>53437600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>48943600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>44907300</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>38532200</v>
+        <v>44221400</v>
       </c>
       <c r="E9" s="3">
+        <v>38487300</v>
+      </c>
+      <c r="F9" s="3">
         <v>45546600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>45514500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>41354100</v>
+      </c>
+      <c r="I9" s="3">
         <v>34790300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>34254600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>36902200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>37403800</v>
       </c>
       <c r="K9" s="3">
         <v>37403800</v>
       </c>
       <c r="L9" s="3">
+        <v>37403800</v>
+      </c>
+      <c r="M9" s="3">
         <v>37662100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>41123000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>39377600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>41994500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>41793800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39764900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>36485600</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5434100</v>
+        <v>5455300</v>
       </c>
       <c r="E10" s="3">
+        <v>5479100</v>
+      </c>
+      <c r="F10" s="3">
         <v>976300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>975600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>3799200</v>
+      </c>
+      <c r="I10" s="3">
         <v>3918100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2944400</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3172000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>8142600</v>
       </c>
       <c r="K10" s="3">
         <v>8142600</v>
       </c>
       <c r="L10" s="3">
+        <v>8142600</v>
+      </c>
+      <c r="M10" s="3">
         <v>8198800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9267200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8873800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11699800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11643900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9178700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8421700</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,58 +909,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1449800</v>
+      </c>
+      <c r="E12" s="3">
         <v>1525400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1423000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1422000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>1398700</v>
+      </c>
+      <c r="I12" s="3">
         <v>1413700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1275000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1373500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1402600</v>
       </c>
       <c r="K12" s="3">
         <v>1402600</v>
       </c>
       <c r="L12" s="3">
+        <v>1402600</v>
+      </c>
+      <c r="M12" s="3">
         <v>1412200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1533100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1468000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1484200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1477100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1381900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1267900</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -997,108 +1013,117 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>591500</v>
+        <v>405600</v>
       </c>
       <c r="E14" s="3">
+        <v>679100</v>
+      </c>
+      <c r="F14" s="3">
         <v>10042300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10035200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>2604800</v>
+      </c>
+      <c r="I14" s="3">
         <v>269100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>575100</v>
-      </c>
-      <c r="I14" s="3">
-        <v>619600</v>
-      </c>
-      <c r="J14" s="3">
-        <v>850700</v>
       </c>
       <c r="K14" s="3">
         <v>850700</v>
       </c>
       <c r="L14" s="3">
+        <v>850700</v>
+      </c>
+      <c r="M14" s="3">
         <v>856600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>356500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>341300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>418100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>416100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>144800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>132900</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1294400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1277500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>992700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>992000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>1397500</v>
+      </c>
+      <c r="I15" s="3">
         <v>1409400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>972200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1047300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1351100</v>
       </c>
       <c r="K15" s="3">
         <v>1351100</v>
       </c>
       <c r="L15" s="3">
+        <v>1351100</v>
+      </c>
+      <c r="M15" s="3">
         <v>1360400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1158900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1109800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1447600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1440700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1098100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1007600</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1114,108 +1139,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>42768400</v>
+        <v>48565100</v>
       </c>
       <c r="E17" s="3">
+        <v>42723400</v>
+      </c>
+      <c r="F17" s="3">
         <v>49839100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>49804100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>44961800</v>
+      </c>
+      <c r="I17" s="3">
         <v>38800300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>38034500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>40974200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>41308800</v>
       </c>
       <c r="K17" s="3">
         <v>41308800</v>
       </c>
       <c r="L17" s="3">
+        <v>41308800</v>
+      </c>
+      <c r="M17" s="3">
         <v>41594000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>45263600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43342500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46222200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>46001200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43608000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40011800</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1198000</v>
+        <v>1111600</v>
       </c>
       <c r="E18" s="3">
+        <v>1242900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3316300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3314000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>191400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-91900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-835500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-900100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>4237700</v>
       </c>
       <c r="K18" s="3">
         <v>4237700</v>
       </c>
       <c r="L18" s="3">
+        <v>4237700</v>
+      </c>
+      <c r="M18" s="3">
         <v>4266900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5126600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4909000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7472200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7436400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5335600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4895600</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1234,258 +1266,274 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-168300</v>
+        <v>-48000</v>
       </c>
       <c r="E20" s="3">
+        <v>-211000</v>
+      </c>
+      <c r="F20" s="3">
         <v>509600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>509200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>466200</v>
+      </c>
+      <c r="I20" s="3">
         <v>153500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>223100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>240400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-98000</v>
       </c>
       <c r="K20" s="3">
         <v>-98000</v>
       </c>
       <c r="L20" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="M20" s="3">
         <v>-98700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>394600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>377900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-14700</v>
       </c>
       <c r="P20" s="3">
         <v>-14700</v>
       </c>
       <c r="Q20" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="R20" s="3">
         <v>203100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>2643800</v>
+        <v>2454000</v>
       </c>
       <c r="E21" s="3">
+        <v>2731500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2833200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2831200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>1122700</v>
+      </c>
+      <c r="I21" s="3">
         <v>1164100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-86400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-93100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>5686800</v>
       </c>
       <c r="K21" s="3">
         <v>5686800</v>
       </c>
       <c r="L21" s="3">
+        <v>5686800</v>
+      </c>
+      <c r="M21" s="3">
         <v>5726100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5890900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5640900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8934500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8891800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6230600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5716800</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>474100</v>
+      </c>
+      <c r="E22" s="3">
         <v>402400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>405700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>405400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>327700</v>
+      </c>
+      <c r="I22" s="3">
         <v>326400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>327200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>352400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>364300</v>
       </c>
       <c r="K22" s="3">
         <v>364300</v>
       </c>
       <c r="L22" s="3">
+        <v>364300</v>
+      </c>
+      <c r="M22" s="3">
         <v>366800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>319400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>305900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>299700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>298200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>345700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>317200</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>571200</v>
+      </c>
+      <c r="E23" s="3">
         <v>620300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13933900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13924100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-2885500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-446400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1530700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1649000</v>
-      </c>
-      <c r="J23" s="3">
-        <v>3744200</v>
       </c>
       <c r="K23" s="3">
         <v>3744200</v>
       </c>
       <c r="L23" s="3">
+        <v>3744200</v>
+      </c>
+      <c r="M23" s="3">
         <v>3770100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4867900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4661300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7429000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7393500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5110100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4688700</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>236500</v>
+      </c>
+      <c r="E24" s="3">
         <v>185600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2148100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2146500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>-690500</v>
+      </c>
+      <c r="I24" s="3">
         <v>-28100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-1465000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-1578200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>719000</v>
       </c>
       <c r="K24" s="3">
         <v>719000</v>
       </c>
       <c r="L24" s="3">
+        <v>719000</v>
+      </c>
+      <c r="M24" s="3">
         <v>723900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>608500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>582700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1469400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1462400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>397600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>364800</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1534,108 +1582,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>334700</v>
+      </c>
+      <c r="E26" s="3">
         <v>434700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11785800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11777500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-2195000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-418300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-65700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-70800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>3025300</v>
       </c>
       <c r="K26" s="3">
         <v>3025300</v>
       </c>
       <c r="L26" s="3">
+        <v>3025300</v>
+      </c>
+      <c r="M26" s="3">
         <v>3046200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4259400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4078600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5959600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5931100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4712500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4323900</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>458900</v>
+        <v>303900</v>
       </c>
       <c r="E27" s="3">
+        <v>449700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-11816400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11808000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-2195000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-401000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-78200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-84200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>3013000</v>
       </c>
       <c r="K27" s="3">
         <v>3013000</v>
       </c>
       <c r="L27" s="3">
+        <v>3013000</v>
+      </c>
+      <c r="M27" s="3">
         <v>3033800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4240600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4060600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5962300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5933800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4723200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4333700</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1684,8 +1741,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1734,8 +1794,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1784,8 +1847,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1834,108 +1900,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>168300</v>
+        <v>48000</v>
       </c>
       <c r="E32" s="3">
+        <v>211000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-509600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-509200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-466200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-153500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-223100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-240400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>98000</v>
       </c>
       <c r="K32" s="3">
         <v>98000</v>
       </c>
       <c r="L32" s="3">
+        <v>98000</v>
+      </c>
+      <c r="M32" s="3">
         <v>98700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-394600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-377900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>14700</v>
       </c>
       <c r="P32" s="3">
         <v>14700</v>
       </c>
       <c r="Q32" s="3">
+        <v>14700</v>
+      </c>
+      <c r="R32" s="3">
         <v>-203100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-186300</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E33" s="3">
         <v>449700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11816400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11808000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-2195000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-401000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-78200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-84200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>3013000</v>
       </c>
       <c r="K33" s="3">
         <v>3013000</v>
       </c>
       <c r="L33" s="3">
+        <v>3013000</v>
+      </c>
+      <c r="M33" s="3">
         <v>3033800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4240600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4060600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5962300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5933800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4723200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4333700</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1984,113 +2059,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E35" s="3">
         <v>449700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11816400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11808000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-2195000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-401000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-78200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-84200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>3013000</v>
       </c>
       <c r="K35" s="3">
         <v>3013000</v>
       </c>
       <c r="L35" s="3">
+        <v>3013000</v>
+      </c>
+      <c r="M35" s="3">
         <v>3033800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4240600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4060600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5962300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5933800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4723200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4333700</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45473</v>
       </c>
       <c r="K38" s="2">
         <v>45473</v>
       </c>
       <c r="L38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2109,8 +2193,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2129,458 +2214,486 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>35664300</v>
+      </c>
+      <c r="E41" s="3">
         <v>34146200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33107900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33084600</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="H41" s="3">
+        <v>34015300</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>33553200</v>
-      </c>
-      <c r="I41" s="3">
-        <v>36146600</v>
-      </c>
-      <c r="J41" s="3">
-        <v>37342800</v>
       </c>
       <c r="K41" s="3">
         <v>37342800</v>
       </c>
       <c r="L41" s="3">
+        <v>37342800</v>
+      </c>
+      <c r="M41" s="3">
         <v>37600600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46887400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44897300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52120100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>51870900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>48450400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>44454800</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>838600</v>
+      </c>
+      <c r="E42" s="3">
         <v>897000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1381900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1381000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>2357000</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>3088300</v>
-      </c>
-      <c r="I42" s="3">
-        <v>3327000</v>
-      </c>
-      <c r="J42" s="3">
-        <v>3443700</v>
       </c>
       <c r="K42" s="3">
         <v>3443700</v>
       </c>
       <c r="L42" s="3">
+        <v>3443700</v>
+      </c>
+      <c r="M42" s="3">
         <v>3467500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5238200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5015900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4986900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4963100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4103900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3765400</v>
       </c>
     </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>18070400</v>
+      </c>
+      <c r="E43" s="3">
         <v>18171300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15473800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15462900</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="H43" s="3">
+        <v>15443300</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>12460900</v>
-      </c>
-      <c r="I43" s="3">
-        <v>13424000</v>
-      </c>
-      <c r="J43" s="3">
-        <v>13939800</v>
       </c>
       <c r="K43" s="3">
         <v>13939800</v>
       </c>
       <c r="L43" s="3">
+        <v>13939800</v>
+      </c>
+      <c r="M43" s="3">
         <v>14036000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12754500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12213200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14342800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14274200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9593900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8802700</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>27404300</v>
+      </c>
+      <c r="E44" s="3">
         <v>28779000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26010300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25992000</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="H44" s="3">
+        <v>25616000</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>21597500</v>
-      </c>
-      <c r="I44" s="3">
-        <v>23266800</v>
-      </c>
-      <c r="J44" s="3">
-        <v>23736200</v>
       </c>
       <c r="K44" s="3">
         <v>23736200</v>
       </c>
       <c r="L44" s="3">
+        <v>23736200</v>
+      </c>
+      <c r="M44" s="3">
         <v>23900100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>23669700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22665100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>21057900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>20957200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>18553000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>17022900</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>6179600</v>
+      </c>
+      <c r="E45" s="3">
         <v>5073200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4716400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4713100</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="H45" s="3">
+        <v>4213700</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3365800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3625900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4073700</v>
       </c>
       <c r="K45" s="3">
         <v>4073700</v>
       </c>
       <c r="L45" s="3">
+        <v>4073700</v>
+      </c>
+      <c r="M45" s="3">
         <v>4101800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2586500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2476700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2753300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2740100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4532400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4158700</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>103259500</v>
+      </c>
+      <c r="E46" s="3">
         <v>103002400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>94561500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>94494900</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="H46" s="3">
+        <v>94567200</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>84458000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>90985900</v>
-      </c>
-      <c r="J46" s="3">
-        <v>93121200</v>
       </c>
       <c r="K46" s="3">
         <v>93121200</v>
       </c>
       <c r="L46" s="3">
+        <v>93121200</v>
+      </c>
+      <c r="M46" s="3">
         <v>93764200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>101160600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>96867100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>103751100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>103255100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>90601700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>83130000</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>10250200</v>
+      </c>
+      <c r="E47" s="3">
         <v>10168300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10153800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10146700</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="3">
+        <v>12111600</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>12307700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>13259000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>14887000</v>
       </c>
       <c r="K47" s="3">
         <v>14887000</v>
       </c>
       <c r="L47" s="3">
+        <v>14887000</v>
+      </c>
+      <c r="M47" s="3">
         <v>14989800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12270400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11749600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6923600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6890500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5680200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5211800</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>52705400</v>
+      </c>
+      <c r="E48" s="3">
         <v>51783700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45429100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45397200</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="H48" s="3">
+        <v>52716400</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>40273300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>43386100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>44892300</v>
       </c>
       <c r="K48" s="3">
         <v>44892300</v>
       </c>
       <c r="L48" s="3">
+        <v>44892300</v>
+      </c>
+      <c r="M48" s="3">
         <v>45202300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35531100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34023100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>39512000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>39323100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34778200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>31910200</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>52290600</v>
+      </c>
+      <c r="E49" s="3">
         <v>52229900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>36616200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>36590400</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>58469800</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>35923000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>38699500</v>
-      </c>
-      <c r="J49" s="3">
-        <v>57426300</v>
       </c>
       <c r="K49" s="3">
         <v>57426300</v>
       </c>
       <c r="L49" s="3">
+        <v>57426300</v>
+      </c>
+      <c r="M49" s="3">
         <v>57822900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>37630200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>36033000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>55777300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>55510600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>37447900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>34359700</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2629,8 +2742,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2679,58 +2795,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>4789200</v>
+      </c>
+      <c r="E52" s="3">
         <v>4591300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9390600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9384000</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="3">
+        <v>4313600</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>9828100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>10587800</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3303300</v>
       </c>
       <c r="K52" s="3">
         <v>3303300</v>
       </c>
       <c r="L52" s="3">
+        <v>3303300</v>
+      </c>
+      <c r="M52" s="3">
         <v>3326100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9866300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9447500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4632100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4610000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8566800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7860400</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2779,58 +2901,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>243828400</v>
+      </c>
+      <c r="E54" s="3">
         <v>239152500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>229133500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>228972200</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="H54" s="3">
+        <v>235682900</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>214936300</v>
-      </c>
-      <c r="I54" s="3">
-        <v>231549200</v>
-      </c>
-      <c r="J54" s="3">
-        <v>221671500</v>
       </c>
       <c r="K54" s="3">
         <v>221671500</v>
       </c>
       <c r="L54" s="3">
+        <v>221671500</v>
+      </c>
+      <c r="M54" s="3">
         <v>223202100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>223419900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>213937300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>216782800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>215746400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>198948400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>182541700</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2849,8 +2977,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2869,308 +2998,327 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>38391400</v>
+      </c>
+      <c r="E57" s="3">
         <v>39084500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35222500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35197700</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="H57" s="3">
+        <v>35140300</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>30732000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>33107300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>35118400</v>
       </c>
       <c r="K57" s="3">
         <v>35118400</v>
       </c>
       <c r="L57" s="3">
+        <v>35118400</v>
+      </c>
+      <c r="M57" s="3">
         <v>35360900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36485000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>34936500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37877700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>37696700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33906200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>31110000</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>18152600</v>
+      </c>
+      <c r="E58" s="3">
         <v>20000000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16613800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16602100</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>15646500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>12639000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>13615900</v>
-      </c>
-      <c r="J58" s="3">
-        <v>11456100</v>
       </c>
       <c r="K58" s="3">
         <v>11456100</v>
       </c>
       <c r="L58" s="3">
+        <v>11456100</v>
+      </c>
+      <c r="M58" s="3">
         <v>11535200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10478600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10033900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10287100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10237900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8231300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7552500</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>23769000</v>
+      </c>
+      <c r="E59" s="3">
         <v>21918600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22136900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22121300</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="H59" s="3">
+        <v>20086900</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>18216200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>19624100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>18339200</v>
       </c>
       <c r="K59" s="3">
         <v>18339200</v>
       </c>
       <c r="L59" s="3">
+        <v>18339200</v>
+      </c>
+      <c r="M59" s="3">
         <v>18465900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17055400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16331500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16748900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16668800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15967700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14650900</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>99607000</v>
+      </c>
+      <c r="E60" s="3">
         <v>99544600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>92449200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>92384100</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="H60" s="3">
+        <v>89148600</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>77840400</v>
-      </c>
-      <c r="I60" s="3">
-        <v>83856800</v>
-      </c>
-      <c r="J60" s="3">
-        <v>81406800</v>
       </c>
       <c r="K60" s="3">
         <v>81406800</v>
       </c>
       <c r="L60" s="3">
+        <v>81406800</v>
+      </c>
+      <c r="M60" s="3">
         <v>81968900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>81728700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>78259900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>80597200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>80211900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>71417100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>65527600</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>41367500</v>
+      </c>
+      <c r="E61" s="3">
         <v>35272700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37375800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37349500</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>32326500</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>25927100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>27931100</v>
-      </c>
-      <c r="J61" s="3">
-        <v>23110500</v>
       </c>
       <c r="K61" s="3">
         <v>23110500</v>
       </c>
       <c r="L61" s="3">
+        <v>23110500</v>
+      </c>
+      <c r="M61" s="3">
         <v>23270000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22131100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21191800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21898500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21793800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20806900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>19091000</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>23922100</v>
+      </c>
+      <c r="E62" s="3">
         <v>25492900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>27060000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27040900</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="H62" s="3">
+        <v>16032900</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>13767500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>14831600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>15305900</v>
       </c>
       <c r="K62" s="3">
         <v>15305900</v>
       </c>
       <c r="L62" s="3">
+        <v>15305900</v>
+      </c>
+      <c r="M62" s="3">
         <v>15411600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15685900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15020100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16798000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16717700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16032900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14710700</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3219,8 +3367,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3269,8 +3420,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3319,58 +3473,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>173296000</v>
+      </c>
+      <c r="E66" s="3">
         <v>168881600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>165729700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>165613000</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="H66" s="3">
+        <v>149337600</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>129922400</v>
-      </c>
-      <c r="I66" s="3">
-        <v>139964300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>133464100</v>
       </c>
       <c r="K66" s="3">
         <v>133464100</v>
       </c>
       <c r="L66" s="3">
+        <v>133464100</v>
+      </c>
+      <c r="M66" s="3">
         <v>134385600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>132649500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>127019500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>132651700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>132017600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>121592400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>111565000</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3389,8 +3549,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3439,8 +3600,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3489,8 +3653,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3539,8 +3706,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3589,58 +3759,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>61610900</v>
+      </c>
+      <c r="E72" s="3">
         <v>61848300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44617800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>44586400</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="H72" s="3">
+        <v>85983600</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>64378300</v>
-      </c>
-      <c r="I72" s="3">
-        <v>69354200</v>
-      </c>
-      <c r="J72" s="3">
-        <v>85520200</v>
       </c>
       <c r="K72" s="3">
         <v>85520200</v>
       </c>
       <c r="L72" s="3">
+        <v>85520200</v>
+      </c>
+      <c r="M72" s="3">
         <v>86110700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>69576700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>66623600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>79093900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78715800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>71372200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>65486400</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3689,8 +3865,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3739,8 +3918,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3789,58 +3971,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>70009100</v>
+      </c>
+      <c r="E76" s="3">
         <v>69789000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>62875400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>62831200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>85868500</v>
+      </c>
+      <c r="I76" s="3">
         <v>88296600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>84576000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>91113100</v>
-      </c>
-      <c r="J76" s="3">
-        <v>87565600</v>
       </c>
       <c r="K76" s="3">
         <v>87565600</v>
       </c>
       <c r="L76" s="3">
+        <v>87565600</v>
+      </c>
+      <c r="M76" s="3">
         <v>88170200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>90298400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>86465900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>83747800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>83347500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>76946700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>70601100</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3889,113 +4077,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45473</v>
       </c>
       <c r="K80" s="2">
         <v>45473</v>
       </c>
       <c r="L80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E81" s="3">
         <v>449700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11816400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11808000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-2195000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-401000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-78200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-84200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>3013000</v>
       </c>
       <c r="K81" s="3">
         <v>3013000</v>
       </c>
       <c r="L81" s="3">
+        <v>3013000</v>
+      </c>
+      <c r="M81" s="3">
         <v>3033800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4240600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4060600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5962300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5933800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4723200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4333700</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4014,58 +4211,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>1397500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1409400</v>
+      </c>
+      <c r="F83" s="3">
         <v>1162600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1252500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1351100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1360400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1494400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1276500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1447600</v>
       </c>
       <c r="K83" s="3">
         <v>1447600</v>
       </c>
       <c r="L83" s="3">
+        <v>1447600</v>
+      </c>
+      <c r="M83" s="3">
         <v>1440700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1399000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1151700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1199000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1274200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1359600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1235500</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4114,8 +4315,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4164,8 +4368,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4214,8 +4421,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4264,8 +4474,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4314,58 +4527,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>-193100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3133900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1387200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1386200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>656500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3076100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1260500</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-1357900</v>
-      </c>
-      <c r="J89" s="3">
-        <v>2126900</v>
       </c>
       <c r="K89" s="3">
         <v>2126900</v>
       </c>
       <c r="L89" s="3">
+        <v>2126900</v>
+      </c>
+      <c r="M89" s="3">
         <v>2141500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5024900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4811600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7310600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7275600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5405600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4959800</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4384,58 +4603,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1594900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1554200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2078200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2076700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-2487400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2517300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-2773100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-2987400</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-3055300</v>
       </c>
       <c r="K91" s="3">
         <v>-3055300</v>
       </c>
       <c r="L91" s="3">
+        <v>-3055300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-3076400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3175600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3040900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2427400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2415800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2485800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2280800</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4484,8 +4707,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4534,58 +4760,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1947900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1516200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2202100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2200500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-1338800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1087300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1645600</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-1772800</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-3710500</v>
       </c>
       <c r="K94" s="3">
         <v>-3710500</v>
       </c>
       <c r="L94" s="3">
+        <v>-3710500</v>
+      </c>
+      <c r="M94" s="3">
         <v>-3736100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5046400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4832200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3229300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3213800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3134000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2875600</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4604,58 +4836,62 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
+        <v>2300600</v>
+      </c>
+      <c r="I96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
-        <v>2491700</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>2491700</v>
       </c>
       <c r="L96" s="3">
+        <v>2491700</v>
+      </c>
+      <c r="M96" s="3">
         <v>2508900</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>2296900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>2286000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>49700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>45600</v>
       </c>
     </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4704,8 +4940,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4754,8 +4993,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4804,154 +5046,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>4027200</v>
+      </c>
+      <c r="E100" s="3">
         <v>6369200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3309300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3306900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-846700</v>
+      </c>
+      <c r="I100" s="3">
         <v>2872900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1848000</v>
-      </c>
-      <c r="I100" s="3">
-        <v>1990900</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-2632100</v>
       </c>
       <c r="K100" s="3">
         <v>-2632100</v>
       </c>
       <c r="L100" s="3">
+        <v>-2632100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-2650200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2599200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2488900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2454700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2443000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1645300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1509600</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-1106300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-317800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-7800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-8400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>227700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>229300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-185700</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-177800</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-272900</v>
       </c>
       <c r="K101" s="3">
         <v>-272900</v>
       </c>
       <c r="L101" s="3">
+        <v>-272900</v>
+      </c>
+      <c r="M101" s="3">
         <v>-271600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-549900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-504500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>855600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>909200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>265000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>270100</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>2000500</v>
+      </c>
+      <c r="E102" s="3">
         <v>2080000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-304700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-304500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-2635300</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1608300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1065800</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-1148200</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-3988000</v>
       </c>
       <c r="K102" s="3">
         <v>-3988000</v>
       </c>
       <c r="L102" s="3">
+        <v>-3988000</v>
+      </c>
+      <c r="M102" s="3">
         <v>-4015500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2806500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2687300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1353700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1347200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>76400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>70100</v>
       </c>
     </row>
